--- a/rtss-pre1917/src/main/resources/1914-war-losses-by-territory.xlsx
+++ b/rtss-pre1917/src/main/resources/1914-war-losses-by-territory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28909F50-68A1-4FBE-81B9-1967A6B87C60}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44449D8-4339-42CE-B404-B3B341E14566}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="1" xr2:uid="{F8F3F2E6-999D-4585-B617-B43779846A3C}"/>
+    <workbookView xWindow="19725" yWindow="1530" windowWidth="16980" windowHeight="20055" activeTab="1" xr2:uid="{F8F3F2E6-999D-4585-B617-B43779846A3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="155">
   <si>
     <t>Акмолинская</t>
   </si>
@@ -499,6 +499,9 @@
   </si>
   <si>
     <t>%потерь</t>
+  </si>
+  <si>
+    <t>% выбывших из строя РСФСР-1991</t>
   </si>
 </sst>
 </file>
@@ -931,7 +934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E734585-A639-4992-9BB6-5D0B3F85270D}">
-  <dimension ref="A1:V99"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -4287,7 +4290,7 @@
         <v>990</v>
       </c>
       <c r="J66" s="9">
-        <f t="shared" ref="J66:J97" si="9">100*I66/ALL_DEATHS</f>
+        <f t="shared" ref="J66:J91" si="9">100*I66/ALL_DEATHS</f>
         <v>1.2660656052177248</v>
       </c>
       <c r="L66" t="s">
@@ -5643,6 +5646,17 @@
       <c r="J99" s="10">
         <f>SUMPRODUCT(B2:B91,J2:J91)</f>
         <v>55.755726069441792</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J101" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J102" s="10">
+        <f>SUMPRODUCT(B2:B91,E2:E91)</f>
+        <v>55.712996318130919</v>
       </c>
     </row>
   </sheetData>

--- a/rtss-pre1917/src/main/resources/1914-war-losses-by-territory.xlsx
+++ b/rtss-pre1917/src/main/resources/1914-war-losses-by-territory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44449D8-4339-42CE-B404-B3B341E14566}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D15BD6-90AA-4A41-B473-0E4CF17C790B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19725" yWindow="1530" windowWidth="16980" windowHeight="20055" activeTab="1" xr2:uid="{F8F3F2E6-999D-4585-B617-B43779846A3C}"/>
   </bookViews>
